--- a/assets/sounds/sounds.xlsx
+++ b/assets/sounds/sounds.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="114">
   <si>
     <t>https://freesound.org/people/schademans/sounds/2597/</t>
   </si>
@@ -355,6 +355,15 @@
   </si>
   <si>
     <t>taploud2.mp3</t>
+  </si>
+  <si>
+    <t>tap.mp3</t>
+  </si>
+  <si>
+    <t>tock2.mp3</t>
+  </si>
+  <si>
+    <t>UNKNOWN — source not identified, please fill in</t>
   </si>
 </sst>
 </file>
@@ -767,15 +776,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{40911E95-D4C8-4A87-AE22-5444E018F219}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:ns4="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{40911E95-D4C8-4A87-AE22-5444E018F219}">
   <dimension ref="A1:B43"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" ns3:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.5703125" customWidth="1"/>
     <col min="2" max="2" width="66.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" ns3:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>61</v>
       </c>
@@ -783,7 +792,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" ns3:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>58</v>
       </c>
@@ -791,7 +800,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" ns3:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>79</v>
       </c>
@@ -799,7 +808,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" ns3:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>80</v>
       </c>
@@ -807,7 +816,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" ns3:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>81</v>
       </c>
@@ -815,7 +824,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" ns3:dyDescent="0.25">
       <c r="A6" s="4" t="s">
         <v>82</v>
       </c>
@@ -823,7 +832,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" ns3:dyDescent="0.25">
       <c r="A7" s="4" t="s">
         <v>39</v>
       </c>
@@ -831,7 +840,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" ns3:dyDescent="0.25">
       <c r="A8" s="4" t="s">
         <v>18</v>
       </c>
@@ -839,7 +848,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" ns3:dyDescent="0.25">
       <c r="A9" s="4" t="s">
         <v>36</v>
       </c>
@@ -847,7 +856,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" ns3:dyDescent="0.25">
       <c r="A10" s="4" t="s">
         <v>42</v>
       </c>
@@ -855,7 +864,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" ns3:dyDescent="0.25">
       <c r="A11" s="4" t="s">
         <v>45</v>
       </c>
@@ -863,7 +872,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" ns3:dyDescent="0.25">
       <c r="A12" s="4" t="s">
         <v>107</v>
       </c>
@@ -871,7 +880,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" ns3:dyDescent="0.25">
       <c r="A13" s="4" t="s">
         <v>109</v>
       </c>
@@ -879,7 +888,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" ns3:dyDescent="0.25">
       <c r="A14" s="4" t="s">
         <v>34</v>
       </c>
@@ -887,7 +896,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" ns3:dyDescent="0.25">
       <c r="A15" s="4" t="s">
         <v>49</v>
       </c>
@@ -895,7 +904,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" ns3:dyDescent="0.25">
       <c r="A16" s="4" t="s">
         <v>101</v>
       </c>
@@ -903,7 +912,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" ns3:dyDescent="0.25">
       <c r="A17" s="4" t="s">
         <v>19</v>
       </c>
@@ -911,7 +920,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" ns3:dyDescent="0.25">
       <c r="A18" s="4" t="s">
         <v>25</v>
       </c>
@@ -919,7 +928,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" ns3:dyDescent="0.25">
       <c r="A19" s="4" t="s">
         <v>11</v>
       </c>
@@ -927,7 +936,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" ns3:dyDescent="0.25">
       <c r="A20" s="4" t="s">
         <v>56</v>
       </c>
@@ -935,7 +944,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" ns3:dyDescent="0.25">
       <c r="A21" s="4" t="s">
         <v>5</v>
       </c>
@@ -943,7 +952,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" ns3:dyDescent="0.25">
       <c r="A22" s="4" t="s">
         <v>9</v>
       </c>
@@ -951,7 +960,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" ns3:dyDescent="0.25">
       <c r="A23" s="4" t="s">
         <v>13</v>
       </c>
@@ -959,7 +968,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" ns3:dyDescent="0.25">
       <c r="A24" s="4" t="s">
         <v>26</v>
       </c>
@@ -967,7 +976,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" ns3:dyDescent="0.25">
       <c r="A25" s="4" t="s">
         <v>47</v>
       </c>
@@ -975,7 +984,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" ns3:dyDescent="0.25">
       <c r="A26" s="4" t="s">
         <v>1</v>
       </c>
@@ -983,7 +992,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" ns3:dyDescent="0.25">
       <c r="A27" s="4" t="s">
         <v>23</v>
       </c>
@@ -991,7 +1000,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" ns3:dyDescent="0.25">
       <c r="A28" s="4" t="s">
         <v>83</v>
       </c>
@@ -999,7 +1008,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" ns3:dyDescent="0.25">
       <c r="A29" s="4" t="s">
         <v>32</v>
       </c>
@@ -1007,7 +1016,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2" ns3:dyDescent="0.25">
       <c r="A30" s="4" t="s">
         <v>106</v>
       </c>
@@ -1015,7 +1024,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2" ns3:dyDescent="0.25">
       <c r="A31" s="4" t="s">
         <v>21</v>
       </c>
@@ -1023,15 +1032,15 @@
         <v>20</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:2" ns3:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="B32" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:2" ns3:dyDescent="0.25">
       <c r="A33" s="4" t="s">
         <v>104</v>
       </c>
@@ -1039,7 +1048,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:2" ns3:dyDescent="0.25">
       <c r="A34" s="4" t="s">
         <v>105</v>
       </c>
@@ -1047,39 +1056,39 @@
         <v>97</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:2" ns3:dyDescent="0.25">
       <c r="A35" s="4" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="B35" s="4" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" ns3:dyDescent="0.25">
+      <c r="A36" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" ns3:dyDescent="0.25">
+      <c r="A37" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="B37" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A36" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="B36" s="4" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A37" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="B37" s="4" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:2" ns3:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>60</v>
+        <v>112</v>
       </c>
       <c r="B38" s="4" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:2" ns3:dyDescent="0.25">
       <c r="A39" s="4" t="s">
         <v>15</v>
       </c>
@@ -1087,7 +1096,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:2" ns3:dyDescent="0.25">
       <c r="A40" s="4" t="s">
         <v>4</v>
       </c>
@@ -1095,43 +1104,45 @@
         <v>3</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:2" ns3:dyDescent="0.25">
       <c r="A41" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B41" s="5"/>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B41" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" ns3:dyDescent="0.25">
       <c r="A42" s="4" t="s">
         <v>40</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" ns3:dyDescent="0.25">
       <c r="A43" s="4" t="s">
         <v>41</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>6</v>
+        <v>113</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B43">
+  <sortState ref="A2:B43">
     <sortCondition ref="A1:A43"/>
   </sortState>
   <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="B21" r:id="rId1" xr:uid="{B0667011-E494-4788-A099-875CB48634BD}"/>
-    <hyperlink ref="B24" r:id="rId2" xr:uid="{31E8F7B0-172D-42B6-987D-6C26CAC96BEB}"/>
-    <hyperlink ref="B10" r:id="rId3" xr:uid="{AFB530BE-2E82-4C72-B0FA-2481A3DD8A62}"/>
-    <hyperlink ref="B3" r:id="rId4" xr:uid="{94B0CBB3-F16C-4B52-A2FA-8D2501FAF799}"/>
-    <hyperlink ref="B4" r:id="rId5" xr:uid="{B40158CA-57FC-4978-9358-958F4E568516}"/>
-    <hyperlink ref="B5" r:id="rId6" xr:uid="{81D4FB89-8E67-4FB4-A78F-EE7AE46E6969}"/>
-    <hyperlink ref="B6" r:id="rId7" xr:uid="{EB4BA6DF-6732-495D-B269-F48B4C557CCF}"/>
-    <hyperlink ref="B20" r:id="rId8" xr:uid="{01BBB744-20F3-4EC1-89D7-3E5F13076559}"/>
-    <hyperlink ref="B28" r:id="rId9" xr:uid="{14BE98D3-1AEC-4E8B-8523-018233783573}"/>
+    <hyperlink ref="B21" ns4:id="rId1" ns2:uid="{B0667011-E494-4788-A099-875CB48634BD}"/>
+    <hyperlink ref="B24" ns4:id="rId2" ns2:uid="{31E8F7B0-172D-42B6-987D-6C26CAC96BEB}"/>
+    <hyperlink ref="B10" ns4:id="rId3" ns2:uid="{AFB530BE-2E82-4C72-B0FA-2481A3DD8A62}"/>
+    <hyperlink ref="B3" ns4:id="rId4" ns2:uid="{94B0CBB3-F16C-4B52-A2FA-8D2501FAF799}"/>
+    <hyperlink ref="B4" ns4:id="rId5" ns2:uid="{B40158CA-57FC-4978-9358-958F4E568516}"/>
+    <hyperlink ref="B5" ns4:id="rId6" ns2:uid="{81D4FB89-8E67-4FB4-A78F-EE7AE46E6969}"/>
+    <hyperlink ref="B6" ns4:id="rId7" ns2:uid="{EB4BA6DF-6732-495D-B269-F48B4C557CCF}"/>
+    <hyperlink ref="B20" ns4:id="rId8" ns2:uid="{01BBB744-20F3-4EC1-89D7-3E5F13076559}"/>
+    <hyperlink ref="B28" ns4:id="rId9" ns2:uid="{14BE98D3-1AEC-4E8B-8523-018233783573}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
